--- a/etf_holdings/2026-08-31_errors.xlsx
+++ b/etf_holdings/2026-08-31_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,20 +441,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2026-08-31 00:58:34</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-31 00:59:35</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>00992A</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-08-31 00:39:45</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:00:35</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
@@ -463,27 +513,77 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-31 00:40:45</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:01:45</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:02:45</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00993A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:03:45</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-08-31_errors.xlsx
+++ b/etf_holdings/2026-08-31_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,24 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-31 00:58:34</t>
+          <t>2026-08-31 01:30:21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00981A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -466,24 +466,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-31 00:59:35</t>
+          <t>2026-08-31 01:31:32</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -491,24 +491,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-31 01:00:35</t>
+          <t>2026-08-31 01:32:32</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00982A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -516,24 +516,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00405A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-31 01:01:45</t>
+          <t>2026-08-31 01:33:32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -541,24 +541,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-31 01:02:45</t>
+          <t>2026-08-31 01:34:32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -566,20 +566,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:35:32</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:36:32</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>00993A</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-08-31 01:03:45</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-31 01:37:51</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:

--- a/etf_holdings/2026-08-31_errors.xlsx
+++ b/etf_holdings/2026-08-31_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-31 01:30:21</t>
+          <t>2026-08-31 17:05:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -466,24 +466,24 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-08-31 01:31:32</t>
+          <t>2026-08-31 17:06:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -491,24 +491,24 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00982A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-31 01:32:32</t>
+          <t>2026-08-31 17:07:01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00982A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -516,24 +516,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-31 01:33:32</t>
+          <t>2026-08-31 17:08:01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00982A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -541,24 +541,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00403A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-31 01:34:32</t>
+          <t>2026-08-31 17:09:01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -566,24 +566,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00992A</t>
+          <t>00985A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-31 01:35:32</t>
+          <t>2026-08-31 17:10:01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -591,24 +591,24 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00992A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-31 01:36:32</t>
+          <t>2026-08-31 17:11:01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
@@ -616,20 +616,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>00405A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:12:12</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:13:12</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
+Call log:
+  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>00993A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-31 01:37:51</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-08-31 17:14:12</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:

--- a/etf_holdings/2026-08-31_errors.xlsx
+++ b/etf_holdings/2026-08-31_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,70 +441,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00981A</t>
+          <t>00980A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-31 17:05:00</t>
+          <t>2026-08-31 22:13:21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00981A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00991A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00991A/holdings</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:06:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00991A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00980A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:07:01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
@@ -513,177 +463,52 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00982A</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00982A/holdings</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:08:01</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-08-31 22:15:01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00982A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00403A</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:09:01</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00403A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00985A</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00985A/holdings</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:10:01</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00985A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00992A</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00992A/holdings</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:11:01</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00992A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>00405A</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:12:12</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-08-31 22:16:01</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
   - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00407A</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00407A/holdings</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:13:12</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00407A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00993A</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00993A/holdings</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-08-31 17:14:12</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00993A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>

--- a/etf_holdings/2026-08-31_errors.xlsx
+++ b/etf_holdings/2026-08-31_errors.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,74 +441,24 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00980A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.etfinfo.tw/etf/00980A/holdings</t>
+          <t>https://www.etfinfo.tw/etf/00981A/holdings</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-08-31 22:13:21</t>
+          <t>2026-08-31 22:21:50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
 Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00980A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>00990A</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00990A/holdings</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-08-31 22:15:01</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00990A/holdings", waiting until "networkidle"
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00405A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>https://www.etfinfo.tw/etf/00405A/holdings</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-08-31 22:16:01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Page.goto: Timeout 60000ms exceeded.
-Call log:
-  - navigating to "https://www.etfinfo.tw/etf/00405A/holdings", waiting until "networkidle"
+  - navigating to "https://www.etfinfo.tw/etf/00981A/holdings", waiting until "networkidle"
 </t>
         </is>
       </c>
